--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_Auto_OV_Fiets.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_Auto_OV_Fiets.xlsx
@@ -6573,7 +6573,7 @@
         <v>365</v>
       </c>
       <c r="B366">
-        <v>0.9538731324761341</v>
+        <v>0.953873132476134</v>
       </c>
       <c r="C366">
         <v>0.9841978813397549</v>
@@ -6590,7 +6590,7 @@
         <v>366</v>
       </c>
       <c r="B367">
-        <v>0.9538731324761341</v>
+        <v>0.953873132476134</v>
       </c>
       <c r="C367">
         <v>0.9841978813397548</v>
@@ -6624,7 +6624,7 @@
         <v>368</v>
       </c>
       <c r="B369">
-        <v>0.9538731324761341</v>
+        <v>0.953873132476134</v>
       </c>
       <c r="C369">
         <v>0.9841978813397548</v>
@@ -7508,7 +7508,7 @@
         <v>420</v>
       </c>
       <c r="B421">
-        <v>0.6413201388771879</v>
+        <v>0.641320138877188</v>
       </c>
       <c r="C421">
         <v>0.6085270168517507</v>
